--- a/Data/examination_dataset1.xlsx
+++ b/Data/examination_dataset1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gnbal\Desktop\Lecture\CorsoR_CadellaPaglia\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gnbal\Desktop\GitHub\MSNeuroLab\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D05D1FE-390C-4FF1-A03F-1210249CE32A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABFD1932-F4C0-4673-9972-5ED976150579}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="17">
   <si>
     <t>age</t>
   </si>
@@ -78,8 +78,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="168" formatCode="0.000"/>
-    <numFmt numFmtId="169" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -123,8 +123,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -429,7 +429,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J151"/>
+  <dimension ref="A1:J147"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -5146,134 +5146,6 @@
         <v>12</v>
       </c>
     </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A148" s="3">
-        <v>30.382444150041</v>
-      </c>
-      <c r="B148" t="s">
-        <v>10</v>
-      </c>
-      <c r="C148" s="2">
-        <v>2.520064949980481</v>
-      </c>
-      <c r="D148" s="2">
-        <v>1453.3285617254519</v>
-      </c>
-      <c r="E148" s="2">
-        <v>0.77261363523832693</v>
-      </c>
-      <c r="F148" s="2">
-        <v>-0.18984663767753951</v>
-      </c>
-      <c r="G148" s="2">
-        <v>1.732895812810767</v>
-      </c>
-      <c r="H148" s="2">
-        <v>3.59668885165028</v>
-      </c>
-      <c r="I148" t="s">
-        <v>11</v>
-      </c>
-      <c r="J148" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A149" s="3">
-        <v>51.879167729758279</v>
-      </c>
-      <c r="B149" t="s">
-        <v>10</v>
-      </c>
-      <c r="C149" s="2">
-        <v>4.9077974865261274</v>
-      </c>
-      <c r="D149" s="2">
-        <v>1529.851361023957</v>
-      </c>
-      <c r="E149" s="2">
-        <v>3.129985039493266</v>
-      </c>
-      <c r="F149" s="2">
-        <v>0.47049273195382529</v>
-      </c>
-      <c r="G149" s="2">
-        <v>4.4036076127336576</v>
-      </c>
-      <c r="H149" s="2">
-        <v>7.679319288457199</v>
-      </c>
-      <c r="I149" t="s">
-        <v>11</v>
-      </c>
-      <c r="J149" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A150" s="3">
-        <v>66.001089405256721</v>
-      </c>
-      <c r="B150" t="s">
-        <v>10</v>
-      </c>
-      <c r="C150" s="2">
-        <v>1.315644975353286</v>
-      </c>
-      <c r="D150" s="2">
-        <v>1404.729185316166</v>
-      </c>
-      <c r="E150" s="2">
-        <v>0.24278844567215141</v>
-      </c>
-      <c r="F150" s="2">
-        <v>-0.95167954301714575</v>
-      </c>
-      <c r="G150" s="2">
-        <v>1.127522319191905</v>
-      </c>
-      <c r="H150" s="2">
-        <v>7.4627556922280647</v>
-      </c>
-      <c r="I150" t="s">
-        <v>11</v>
-      </c>
-      <c r="J150" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A151" s="3">
-        <v>32.129695239648207</v>
-      </c>
-      <c r="B151" t="s">
-        <v>10</v>
-      </c>
-      <c r="C151" s="2">
-        <v>1.490671887270709</v>
-      </c>
-      <c r="D151" s="2">
-        <v>1566.754057865239</v>
-      </c>
-      <c r="E151" s="2">
-        <v>4.6837164490025449</v>
-      </c>
-      <c r="F151" s="2">
-        <v>1.1579104665686411</v>
-      </c>
-      <c r="G151" s="2">
-        <v>1.857653356153274</v>
-      </c>
-      <c r="H151" s="2">
-        <v>5.0958987588175404</v>
-      </c>
-      <c r="I151" t="s">
-        <v>14</v>
-      </c>
-      <c r="J151" t="s">
-        <v>12</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Data/examination_dataset1.xlsx
+++ b/Data/examination_dataset1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gnbal\Desktop\GitHub\MSNeuroLab\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABFD1932-F4C0-4673-9972-5ED976150579}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{028806E0-6E20-42A0-B586-6B5093F9F621}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
